--- a/49916_Cuenca_Aguaytia/_raw_reportes_xlsx/IDConfig_67564_completo.xlsx
+++ b/49916_Cuenca_Aguaytia/_raw_reportes_xlsx/IDConfig_67564_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd22b13deee6d4cc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rde37c4f0faeb48de"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,1161 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    172.6242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    102.2656</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    178.6390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    104.7027</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.4560</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     92.7324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    149.4260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    152.2505</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    611.1720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    107.1614</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.7773</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    253.9957</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    216.5352</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    340.1632</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     92.7324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.9743</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     81.3001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     83.5436</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    104.7027</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.7773</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    149.4260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    233.2399</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    812.9906</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     79.0782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     79.0782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.0577</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     70.4058</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     79.0782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    160.8530</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    279.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     85.8085</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     79.0782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.0577</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    114.6663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     70.4058</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.0778</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     74.6990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    138.3434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     81.3001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.1988</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     81.3001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    132.9312</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    236.6454</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     74.6990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.0778</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    149.4260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     76.8779</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.2312</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.5985</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.5985</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.0577</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     54.0940</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     76.8779</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.6415</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    157.9639</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.4560</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     83.5436</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     92.7324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     99.8501</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    102.2656</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.4560</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    114.6663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    301.7382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     99.8501</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    157.9639</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    169.6491</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    143.8416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    305.9734</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    305.9734</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    335.8603</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    203.5588</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     99.8501</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>20/07/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.9976</x:v>
+        <x:v>    122.3650</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.1432</x:v>
+        <x:v>    124.9743</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.9976</x:v>
+        <x:v>    117.2110</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7000</x:v>
+        <x:v>     85.8085</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7320</x:v>
+        <x:v>    178.6390</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.8712</x:v>
+        <x:v>    166.6956</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7320</x:v>
+        <x:v>    178.6390</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    215.6584</x:v>
+        <x:v>    379.2470</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    267.3944</x:v>
+        <x:v>    423.3871</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.2952</x:v>
+        <x:v>    152.2505</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1569,22 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7320</x:v>
+        <x:v>    178.6390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.9743</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.8584</x:v>
+        <x:v>    127.6050</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.2824</x:v>
+        <x:v>    114.6663</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.9976</x:v>
+        <x:v>    117.2110</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.7256</x:v>
+        <x:v>    157.9639</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.8648</x:v>
+        <x:v>    146.6231</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7320</x:v>
+        <x:v>    194.0525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7000</x:v>
+        <x:v>     85.8085</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>     97.4560</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.5736</x:v>
+        <x:v>    130.2573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.7256</x:v>
+        <x:v>    157.9639</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4280</x:v>
+        <x:v>    122.3650</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.1432</x:v>
+        <x:v>    178.6390</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.4472</x:v>
+        <x:v>    181.6787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    215.6584</x:v>
+        <x:v>    379.2470</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.4472</x:v>
+        <x:v>    181.6787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7320</x:v>
+        <x:v>    178.6390</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.7064</x:v>
+        <x:v>    102.2656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.9976</x:v>
+        <x:v>    117.2110</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.4472</x:v>
+        <x:v>    181.6787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.8712</x:v>
+        <x:v>    166.6956</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.2824</x:v>
+        <x:v>    114.6663</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7320</x:v>
+        <x:v>    178.6390</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.2824</x:v>
+        <x:v>    114.6663</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.4472</x:v>
+        <x:v>    181.6787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7320</x:v>
+        <x:v>    178.6390</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    189.7904</x:v>
+        <x:v>    357.4556</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +1989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.4472</x:v>
+        <x:v>    181.6787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +2004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.7192</x:v>
+        <x:v>    138.3434</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +2019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.8712</x:v>
+        <x:v>    166.6956</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +2034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    119.7576</x:v>
+        <x:v>    271.8840</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +2049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4280</x:v>
+        <x:v>    122.3650</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +2064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.8456</x:v>
+        <x:v>     92.7324</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +2079,37 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.0104</x:v>
+        <x:v>    155.0964</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    160.8530</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    194.0525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +2124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.1304</x:v>
+        <x:v>    166.6956</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +2139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.1368</x:v>
+        <x:v>    107.1614</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +2154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.8456</x:v>
+        <x:v>     92.7324</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +2169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.1560</x:v>
+        <x:v>    163.7635</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +2184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    107.7512</x:v>
+        <x:v>    246.9911</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +2199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>    107.1614</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +2214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.2696</x:v>
+        <x:v>     81.3001</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +2229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.2824</x:v>
+        <x:v>    114.6663</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +2244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7000</x:v>
+        <x:v>     85.8085</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +2259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.5800</x:v>
+        <x:v>    149.4260</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +2274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.8520</x:v>
+        <x:v>    109.6415</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +2289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.1368</x:v>
+        <x:v>    107.1614</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +2304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4280</x:v>
+        <x:v>    122.3650</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +2319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.3080</x:v>
+        <x:v>    194.0525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +2334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     82.0232</x:v>
+        <x:v>    197.1998</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +2349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    143.2280</x:v>
+        <x:v>    318.7312</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +2364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     82.0232</x:v>
+        <x:v>    197.1998</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +2379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4280</x:v>
+        <x:v>    122.3650</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +2394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.0104</x:v>
+        <x:v>    155.0964</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +2409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.1432</x:v>
+        <x:v>    124.9743</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +2424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0040</x:v>
+        <x:v>    135.6265</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +2439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.5864</x:v>
+        <x:v>    169.6491</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +2454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    194.9640</x:v>
+        <x:v>    361.7984</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +2469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    355.3456</x:v>
+        <x:v>    499.9996</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +2484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    127.7072</x:v>
+        <x:v>    305.9734</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +2499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     94.0296</x:v>
+        <x:v>    219.8331</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +2514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.5800</x:v>
+        <x:v>    149.4260</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +2529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7320</x:v>
+        <x:v>    178.6390</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +2544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.3016</x:v>
+        <x:v>    172.6242</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1359,7 +2559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.4408</x:v>
+        <x:v>    160.8530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +2574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    194.9640</x:v>
+        <x:v>    361.7984</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +2589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.5928</x:v>
+        <x:v>    190.9268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1404,7 +2604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7320</x:v>
+        <x:v>    178.6390</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1419,7 +2619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.5800</x:v>
+        <x:v>    149.4260</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1434,7 +2634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    194.9640</x:v>
+        <x:v>    361.7984</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +2649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    184.6168</x:v>
+        <x:v>    353.1205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +2664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.7384</x:v>
+        <x:v>    200.3685</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +2679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.3016</x:v>
+        <x:v>    172.6242</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +2694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    100.8904</x:v>
+        <x:v>    233.2399</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1509,7 +2709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     76.8776</x:v>
+        <x:v>    187.8225</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1524,7 +2724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    121.4728</x:v>
+        <x:v>    275.5263</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1539,7 +2739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    438.1232</x:v>
+        <x:v>    573.7485</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1554,7 +2754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.1624</x:v>
+        <x:v>    184.7398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1569,7 +2769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    102.6056</x:v>
+        <x:v>    236.6454</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1584,7 +2784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    650.2408</x:v>
+        <x:v>    769.0370</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1599,7 +2799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    100.8904</x:v>
+        <x:v>    233.2399</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1614,7 +2814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    608.8520</x:v>
+        <x:v>    730.2782</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1629,7 +2829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    100.8904</x:v>
+        <x:v>    233.2399</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1644,7 +2844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    109.4664</x:v>
+        <x:v>    250.4826</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1659,7 +2859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.4536</x:v>
+        <x:v>    203.5588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1674,7 +2874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    114.6120</x:v>
+        <x:v>    261.0865</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1689,7 +2889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    153.5752</x:v>
+        <x:v>    327.2791</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +2904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.2952</x:v>
+        <x:v>    152.2505</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1719,7 +2919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    100.8904</x:v>
+        <x:v>    233.2399</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1734,7 +2934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     76.8776</x:v>
+        <x:v>    187.8225</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1749,7 +2949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    112.8968</x:v>
+        <x:v>    257.5304</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1764,7 +2964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.5800</x:v>
+        <x:v>    149.4260</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1779,7 +2979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.4536</x:v>
+        <x:v>    203.5588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1794,7 +2994,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7320</x:v>
+        <x:v>    178.6390</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1809,7 +3009,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    153.5752</x:v>
+        <x:v>    327.2791</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1824,7 +3024,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     87.1688</x:v>
+        <x:v>    206.7707</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1839,7 +3039,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.3080</x:v>
+        <x:v>    194.0525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1854,7 +3054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.3080</x:v>
+        <x:v>    194.0525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1869,7 +3069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.3016</x:v>
+        <x:v>    172.6242</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +3084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.4536</x:v>
+        <x:v>    203.5588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1899,7 +3099,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.4536</x:v>
+        <x:v>    203.5588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1914,7 +3114,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    257.0472</x:v>
+        <x:v>    414.5016</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1929,7 +3129,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    127.7072</x:v>
+        <x:v>    305.9734</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1944,7 +3144,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.4536</x:v>
+        <x:v>    203.5588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1959,7 +3159,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    391.5608</x:v>
+        <x:v>    532.0785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1974,7 +3174,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.3080</x:v>
+        <x:v>    194.0525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1989,7 +3189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.0168</x:v>
+        <x:v>    175.6209</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2004,7 +3204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    100.8904</x:v>
+        <x:v>    233.2399</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2019,7 +3219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.1624</x:v>
+        <x:v>    184.7398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2034,7 +3234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    143.2280</x:v>
+        <x:v>    318.7312</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2049,7 +3249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    100.8904</x:v>
+        <x:v>    233.2399</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2064,7 +3264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    184.6168</x:v>
+        <x:v>    353.1205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2079,7 +3279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.4536</x:v>
+        <x:v>    203.5588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2094,7 +3294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    109.4664</x:v>
+        <x:v>    250.4826</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2109,7 +3309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.7384</x:v>
+        <x:v>    200.3685</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2124,7 +3324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     97.4600</x:v>
+        <x:v>    226.4935</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2139,7 +3339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    344.9984</x:v>
+        <x:v>    490.8894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2154,7 +3354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    344.9984</x:v>
+        <x:v>    490.8894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2169,7 +3369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    226.0056</x:v>
+        <x:v>    388.0167</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2184,7 +3384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    339.8248</x:v>
+        <x:v>    486.3437</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2199,7 +3399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     82.0232</x:v>
+        <x:v>    197.1998</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2214,7 +3414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.0360</x:v>
+        <x:v>    243.5210</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2229,7 +3429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     82.0232</x:v>
+        <x:v>    197.1998</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2244,7 +3444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     82.0232</x:v>
+        <x:v>    197.1998</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2259,7 +3459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.0168</x:v>
+        <x:v>    175.6209</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2274,7 +3474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    119.7576</x:v>
+        <x:v>    271.8840</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2289,7 +3489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    200.1376</x:v>
+        <x:v>    366.1491</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2304,7 +3504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7320</x:v>
+        <x:v>    178.6390</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2319,7 +3519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.4536</x:v>
+        <x:v>    203.5588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2334,7 +3534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.5928</x:v>
+        <x:v>    190.9268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2349,7 +3549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.4536</x:v>
+        <x:v>    203.5588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2364,7 +3564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.3080</x:v>
+        <x:v>    194.0525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2379,7 +3579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.7384</x:v>
+        <x:v>    200.3685</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2394,7 +3594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    132.8808</x:v>
+        <x:v>    310.2173</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2409,7 +3609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.0360</x:v>
+        <x:v>    243.5210</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2424,7 +3624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    118.0424</x:v>
+        <x:v>    268.2633</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2439,7 +3639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     87.1688</x:v>
+        <x:v>    206.7707</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2454,7 +3654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.4536</x:v>
+        <x:v>    203.5588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2469,7 +3669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.7384</x:v>
+        <x:v>    200.3685</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2484,7 +3684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.0360</x:v>
+        <x:v>    243.5210</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2499,7 +3699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    246.7000</x:v>
+        <x:v>    405.6445</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2514,7 +3714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    226.0056</x:v>
+        <x:v>    388.0167</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2529,7 +3729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    427.7760</x:v>
+        <x:v>    564.4483</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2544,7 +3744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.5800</x:v>
+        <x:v>    149.4260</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2559,7 +3759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.5800</x:v>
+        <x:v>    149.4260</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2574,7 +3774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.4536</x:v>
+        <x:v>    203.5588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2589,7 +3789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.7256</x:v>
+        <x:v>    157.9639</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2604,7 +3804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.1624</x:v>
+        <x:v>    184.7398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2619,7 +3819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.5928</x:v>
+        <x:v>    190.9268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2634,7 +3834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.7384</x:v>
+        <x:v>    200.3685</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2649,7 +3849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.4536</x:v>
+        <x:v>    203.5588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2664,7 +3864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    329.4776</x:v>
+        <x:v>    477.2712</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2679,7 +3879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    474.3384</x:v>
+        <x:v>    606.4749</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2694,7 +3894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.7384</x:v>
+        <x:v>    200.3685</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2709,7 +3909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    143.2280</x:v>
+        <x:v>    318.7312</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2724,7 +3924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    453.6440</x:v>
+        <x:v>    587.7410</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2739,7 +3939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     88.8840</x:v>
+        <x:v>    210.0040</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2754,7 +3954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    453.6440</x:v>
+        <x:v>    587.7410</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2769,7 +3969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.7384</x:v>
+        <x:v>    200.3685</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2784,7 +3984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    112.8968</x:v>
+        <x:v>    257.5304</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2799,7 +3999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    112.8968</x:v>
+        <x:v>    257.5304</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2814,7 +4014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    474.3384</x:v>
+        <x:v>    606.4749</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2829,7 +4029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    114.6120</x:v>
+        <x:v>    261.0865</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2844,7 +4044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     92.3144</x:v>
+        <x:v>    216.5352</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2859,7 +4059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    104.3208</x:v>
+        <x:v>    240.0725</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2874,7 +4074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    100.8904</x:v>
+        <x:v>    233.2399</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2889,7 +4089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    107.7512</x:v>
+        <x:v>    246.9911</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2904,7 +4104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    267.3944</x:v>
+        <x:v>    423.3871</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2919,7 +4119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    686.4560</x:v>
+        <x:v>    803.1918</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2934,7 +4134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     99.1752</x:v>
+        <x:v>    229.8560</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2949,7 +4149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.5928</x:v>
+        <x:v>    190.9268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2964,7 +4164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.7384</x:v>
+        <x:v>    200.3685</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2979,7 +4179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.5928</x:v>
+        <x:v>    190.9268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2994,7 +4194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     97.4600</x:v>
+        <x:v>    226.4935</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3009,7 +4209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    324.3040</x:v>
+        <x:v>    472.7446</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3024,7 +4224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    163.9224</x:v>
+        <x:v>    335.8603</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3039,7 +4239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    939.9624</x:v>
+        <x:v>   1048.0443</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3054,7 +4254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    453.6440</x:v>
+        <x:v>    587.7410</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3069,7 +4269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    169.0960</x:v>
+        <x:v>    340.1632</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3084,7 +4284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    184.6168</x:v>
+        <x:v>    353.1205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3099,7 +4299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     82.0232</x:v>
+        <x:v>    197.1998</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3114,7 +4314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    163.9224</x:v>
+        <x:v>    335.8603</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3129,7 +4329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.3016</x:v>
+        <x:v>    172.6242</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3144,7 +4344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     90.5992</x:v>
+        <x:v>    213.2589</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3159,7 +4359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    412.2552</x:v>
+        <x:v>    550.5407</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3174,7 +4374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.0168</x:v>
+        <x:v>    175.6209</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3189,7 +4389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     97.4600</x:v>
+        <x:v>    226.4935</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3204,7 +4404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    107.7512</x:v>
+        <x:v>    246.9911</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3219,7 +4419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     99.1752</x:v>
+        <x:v>    229.8560</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3234,7 +4434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    432.9496</x:v>
+        <x:v>    569.0956</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3249,7 +4449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    148.4016</x:v>
+        <x:v>    323.0009</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3264,7 +4464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    143.2280</x:v>
+        <x:v>    318.7312</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3279,7 +4479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    453.6440</x:v>
+        <x:v>    587.7410</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3294,7 +4494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    396.7344</x:v>
+        <x:v>    536.6853</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3309,7 +4509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    639.8936</x:v>
+        <x:v>    759.3194</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3324,7 +4524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    691.6296</x:v>
+        <x:v>    808.0890</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3339,7 +4539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    184.6168</x:v>
+        <x:v>    353.1205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3354,7 +4554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.3080</x:v>
+        <x:v>    194.0525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3369,7 +4569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.4536</x:v>
+        <x:v>    203.5588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3384,7 +4584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.0360</x:v>
+        <x:v>    243.5210</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3399,7 +4599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.0360</x:v>
+        <x:v>    243.5210</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3414,7 +4614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.7384</x:v>
+        <x:v>    200.3685</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3429,7 +4629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.0360</x:v>
+        <x:v>    243.5210</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3444,7 +4644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    123.1880</x:v>
+        <x:v>    297.5118</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3459,7 +4659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    118.0424</x:v>
+        <x:v>    268.2633</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3474,7 +4674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    531.2480</x:v>
+        <x:v>    658.4343</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3489,7 +4689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.0360</x:v>
+        <x:v>    243.5210</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3504,7 +4704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    143.2280</x:v>
+        <x:v>    318.7312</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3519,7 +4719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    205.3112</x:v>
+        <x:v>    370.5074</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3534,7 +4734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.3080</x:v>
+        <x:v>    194.0525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3549,7 +4749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.5928</x:v>
+        <x:v>    190.9268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3564,7 +4764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.1624</x:v>
+        <x:v>    184.7398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3579,7 +4779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    121.4728</x:v>
+        <x:v>    275.5263</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3594,7 +4794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.5928</x:v>
+        <x:v>    190.9268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3609,7 +4809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    163.9224</x:v>
+        <x:v>    335.8603</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3624,7 +4824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     95.7448</x:v>
+        <x:v>    223.1526</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3639,7 +4839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    138.0544</x:v>
+        <x:v>    314.4700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3654,7 +4854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.3080</x:v>
+        <x:v>    194.0525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3669,7 +4869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     95.7448</x:v>
+        <x:v>    223.1526</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3684,7 +4884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.3080</x:v>
+        <x:v>    194.0525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3699,7 +4899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    138.0544</x:v>
+        <x:v>    314.4700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3714,7 +4914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.1624</x:v>
+        <x:v>    184.7398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3729,7 +4929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     88.8840</x:v>
+        <x:v>    210.0040</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3744,7 +4944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    102.6056</x:v>
+        <x:v>    236.6454</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3759,7 +4959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    118.0424</x:v>
+        <x:v>    268.2633</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3774,7 +4974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.0168</x:v>
+        <x:v>    175.6209</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3789,7 +4989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.7384</x:v>
+        <x:v>    200.3685</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3804,7 +5004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.1624</x:v>
+        <x:v>    184.7398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3819,7 +5019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     94.0296</x:v>
+        <x:v>    219.8331</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3834,7 +5034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    417.4288</x:v>
+        <x:v>    555.1708</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3849,7 +5049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    324.3040</x:v>
+        <x:v>    472.7446</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3864,7 +5064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    205.3112</x:v>
+        <x:v>    370.5074</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3879,7 +5079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    127.7072</x:v>
+        <x:v>    305.9734</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3894,7 +5094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.1560</x:v>
+        <x:v>    163.7635</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3909,7 +5109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.4536</x:v>
+        <x:v>    203.5588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3924,7 +5124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    350.1720</x:v>
+        <x:v>    495.4414</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3939,7 +5139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    109.4664</x:v>
+        <x:v>    250.4826</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3954,7 +5154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.4536</x:v>
+        <x:v>    203.5588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3969,7 +5169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     92.3144</x:v>
+        <x:v>    216.5352</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3984,7 +5184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.4536</x:v>
+        <x:v>    203.5588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3999,7 +5199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    241.5264</x:v>
+        <x:v>    401.2266</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4014,7 +5214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    246.7000</x:v>
+        <x:v>    405.6445</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4029,7 +5229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.0168</x:v>
+        <x:v>    175.6209</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4044,7 +5244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.0168</x:v>
+        <x:v>    175.6209</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4059,7 +5259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.1560</x:v>
+        <x:v>    163.7635</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4074,7 +5274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     94.0296</x:v>
+        <x:v>    219.8331</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4089,7 +5289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    396.7344</x:v>
+        <x:v>    536.6853</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4104,7 +5304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     99.1752</x:v>
+        <x:v>    229.8560</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4119,7 +5319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    215.6584</x:v>
+        <x:v>    379.2470</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4134,7 +5334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    370.8664</x:v>
+        <x:v>    513.7113</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4149,7 +5349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    370.8664</x:v>
+        <x:v>    513.7113</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4164,7 +5364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    104.3208</x:v>
+        <x:v>    240.0725</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4179,7 +5379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    118.0424</x:v>
+        <x:v>    268.2633</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4194,7 +5394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>   1110.6912</x:v>
+        <x:v>   1218.0445</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4209,7 +5409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    118.0424</x:v>
+        <x:v>    284.8865</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4224,7 +5424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    132.8808</x:v>
+        <x:v>    310.2173</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4239,7 +5439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.1432</x:v>
+        <x:v>    103.0958</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4254,7 +5454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.1432</x:v>
+        <x:v>    103.0958</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4269,7 +5469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     90.5992</x:v>
+        <x:v>    219.0195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4284,7 +5484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    102.6056</x:v>
+        <x:v>    247.5185</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4299,7 +5499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.0104</x:v>
+        <x:v>    143.6141</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4314,7 +5514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.4408</x:v>
+        <x:v>    151.2848</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4329,7 +5529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.8648</x:v>
+        <x:v>    132.2832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4344,7 +5544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.1560</x:v>
+        <x:v>    155.1552</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4359,7 +5559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.4472</x:v>
+        <x:v>    178.8683</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4374,7 +5574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    116.3272</x:v>
+        <x:v>    280.6964</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4389,7 +5589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.4472</x:v>
+        <x:v>    178.8683</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4404,7 +5604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    143.2280</x:v>
+        <x:v>    318.7312</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4419,7 +5619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    458.8176</x:v>
+        <x:v>    592.4162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4434,7 +5634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.8712</x:v>
+        <x:v>    159.0489</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4449,7 +5649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.5736</x:v>
+        <x:v>    110.2524</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4464,7 +5664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.3080</x:v>
+        <x:v>    195.1444</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4479,7 +5679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     87.1688</x:v>
+        <x:v>    210.9745</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4494,7 +5694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    396.7344</x:v>
+        <x:v>    536.6853</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4509,7 +5709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.4472</x:v>
+        <x:v>    178.8683</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4524,7 +5724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.8584</x:v>
+        <x:v>    106.6624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4539,7 +5739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.8648</x:v>
+        <x:v>    132.2832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4554,7 +5754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.0168</x:v>
+        <x:v>    170.8705</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4569,7 +5769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    329.4776</x:v>
+        <x:v>    477.2712</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4584,7 +5784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0040</x:v>
+        <x:v>    117.5026</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4599,7 +5799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.4408</x:v>
+        <x:v>    151.2848</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4614,7 +5814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.1240</x:v>
+        <x:v>     33.5937</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4629,7 +5829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.7128</x:v>
+        <x:v>     96.0326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4644,7 +5844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4280</x:v>
+        <x:v>     99.5525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4659,7 +5859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.8520</x:v>
+        <x:v>     82.1866</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4674,7 +5874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.7128</x:v>
+        <x:v>     96.0326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4689,7 +5889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.8584</x:v>
+        <x:v>    106.6624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4704,7 +5904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.5800</x:v>
+        <x:v>    136.0368</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4719,7 +5919,22 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    639.8936</x:v>
+        <x:v>    759.3194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.5119</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4734,7 +5949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8392</x:v>
+        <x:v>     36.6697</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4749,7 +5964,67 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.5672</x:v>
+        <x:v>     85.6130</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.5644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.5235</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.5235</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.5644</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4764,7 +6039,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4088</x:v>
+        <x:v>     30.5411</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4779,7 +6054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.1240</x:v>
+        <x:v>     33.5937</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4794,7 +6069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.9848</x:v>
+        <x:v>     46.0377</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4809,7 +6084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.1240</x:v>
+        <x:v>     33.5937</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4824,7 +6099,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.5608</x:v>
+        <x:v>     62.1185</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4839,7 +6114,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.1368</x:v>
+        <x:v>     78.7835</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4854,7 +6129,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>     65.4048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4869,7 +6144,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.9912</x:v>
+        <x:v>     68.7144</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4884,7 +6159,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.7128</x:v>
+        <x:v>     96.0326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4899,7 +6174,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    114.6120</x:v>
+        <x:v>    276.5155</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4914,7 +6189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8392</x:v>
+        <x:v>     36.6697</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4929,7 +6204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7000</x:v>
+        <x:v>     49.2072</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4944,7 +6219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4280</x:v>
+        <x:v>     99.5525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4959,7 +6234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.9976</x:v>
+        <x:v>     92.5360</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4974,7 +6249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.8456</x:v>
+        <x:v>     58.8557</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4989,7 +6264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.5608</x:v>
+        <x:v>     62.1185</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5004,7 +6279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.5608</x:v>
+        <x:v>     62.1185</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5019,7 +6294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7000</x:v>
+        <x:v>     49.2072</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5034,7 +6309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.1304</x:v>
+        <x:v>     55.6161</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5049,7 +6324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.1368</x:v>
+        <x:v>     78.7835</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5064,7 +6339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.2824</x:v>
+        <x:v>     89.0628</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5079,7 +6354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.8712</x:v>
+        <x:v>    159.0489</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5094,7 +6369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>     65.4048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5109,7 +6384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.5608</x:v>
+        <x:v>     62.1185</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5124,7 +6399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.9912</x:v>
+        <x:v>     68.7144</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5139,7 +6414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.7128</x:v>
+        <x:v>     96.0326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5154,7 +6429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.2824</x:v>
+        <x:v>     89.0628</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5169,7 +6444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.2824</x:v>
+        <x:v>     89.0628</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5184,7 +6459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.7064</x:v>
+        <x:v>     72.0474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5199,7 +6474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.2824</x:v>
+        <x:v>     89.0628</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5214,7 +6489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.7128</x:v>
+        <x:v>     96.0326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5229,7 +6504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.8648</x:v>
+        <x:v>    132.2832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5244,7 +6519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    153.5752</x:v>
+        <x:v>    327.2791</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5259,7 +6534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>     65.4048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5274,7 +6549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.9976</x:v>
+        <x:v>     92.5360</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5289,7 +6564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.1432</x:v>
+        <x:v>    103.0958</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5304,7 +6579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.1496</x:v>
+        <x:v>    128.5530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5319,7 +6594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.8648</x:v>
+        <x:v>    132.2832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5334,7 +6609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>     65.4048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5349,7 +6624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.7128</x:v>
+        <x:v>     96.0326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5364,7 +6639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.0104</x:v>
+        <x:v>    143.6141</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5379,7 +6654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.3016</x:v>
+        <x:v>    166.9066</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5394,7 +6669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.5736</x:v>
+        <x:v>    110.2524</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5409,7 +6684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.7384</x:v>
+        <x:v>    202.9749</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5424,7 +6699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.7192</x:v>
+        <x:v>    121.1627</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5439,7 +6714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     99.1752</x:v>
+        <x:v>    239.3233</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5454,7 +6729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.7256</x:v>
+        <x:v>    147.4377</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5469,7 +6744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.2888</x:v>
+        <x:v>    113.8658</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5484,7 +6759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.9976</x:v>
+        <x:v>     92.5360</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5499,7 +6774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.8520</x:v>
+        <x:v>     82.1866</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5514,7 +6789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.1432</x:v>
+        <x:v>    103.0958</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5529,7 +6804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.5608</x:v>
+        <x:v>     62.1185</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5544,7 +6819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7000</x:v>
+        <x:v>     49.2072</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5559,7 +6834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.7064</x:v>
+        <x:v>     72.0474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5574,7 +6849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>     65.4048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5589,7 +6864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>     65.4048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5604,7 +6879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.7064</x:v>
+        <x:v>     72.0474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5619,7 +6894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.9912</x:v>
+        <x:v>     68.7144</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5634,7 +6909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.8648</x:v>
+        <x:v>    132.2832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5649,7 +6924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.2824</x:v>
+        <x:v>     89.0628</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5664,7 +6939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.3016</x:v>
+        <x:v>    166.9066</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5679,7 +6954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.4152</x:v>
+        <x:v>     52.4000</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5694,7 +6969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7000</x:v>
+        <x:v>     49.2072</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5709,7 +6984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.4152</x:v>
+        <x:v>     52.4000</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5724,7 +6999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7000</x:v>
+        <x:v>     49.2072</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5739,7 +7014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>     65.4048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5754,7 +7029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>     65.4048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5769,7 +7044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.5608</x:v>
+        <x:v>     62.1185</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5784,7 +7059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>     65.4048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5799,7 +7074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>     65.4048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5814,7 +7089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.9912</x:v>
+        <x:v>     68.7144</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5829,7 +7104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.7128</x:v>
+        <x:v>     96.0326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5844,7 +7119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4280</x:v>
+        <x:v>     99.5525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5859,7 +7134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4280</x:v>
+        <x:v>     99.5525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5874,7 +7149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.1496</x:v>
+        <x:v>    128.5530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5889,7 +7164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.3080</x:v>
+        <x:v>    195.1444</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5904,7 +7179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.0360</x:v>
+        <x:v>    255.7543</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5919,7 +7194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.5736</x:v>
+        <x:v>    110.2524</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5934,7 +7209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.5736</x:v>
+        <x:v>    110.2524</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5949,7 +7224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.1496</x:v>
+        <x:v>    128.5530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5964,7 +7239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.7192</x:v>
+        <x:v>    121.1627</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5979,7 +7254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.8648</x:v>
+        <x:v>    132.2832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5994,7 +7269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.7256</x:v>
+        <x:v>    147.4377</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6009,7 +7284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.4408</x:v>
+        <x:v>    151.2848</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6024,7 +7299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.3016</x:v>
+        <x:v>    166.9066</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6039,7 +7314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.5800</x:v>
+        <x:v>    136.0368</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6054,7 +7329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.2888</x:v>
+        <x:v>    113.8658</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6069,7 +7344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.5736</x:v>
+        <x:v>    110.2524</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6084,7 +7359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.8648</x:v>
+        <x:v>    132.2832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6099,7 +7374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.3080</x:v>
+        <x:v>    195.1444</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6114,7 +7389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     97.4600</x:v>
+        <x:v>    235.2412</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6129,7 +7404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     94.0296</x:v>
+        <x:v>    227.1088</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6144,7 +7419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    324.3040</x:v>
+        <x:v>    472.7446</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6159,7 +7434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.1624</x:v>
+        <x:v>    182.9023</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6174,7 +7449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.7192</x:v>
+        <x:v>    121.1627</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6189,7 +7464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.4408</x:v>
+        <x:v>    151.2848</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6204,7 +7479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.0168</x:v>
+        <x:v>    170.8705</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6219,7 +7494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    696.8032</x:v>
+        <x:v>    812.9906</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6234,7 +7509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.1432</x:v>
+        <x:v>    103.0958</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6249,7 +7524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.1368</x:v>
+        <x:v>     78.7835</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6264,7 +7539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.1368</x:v>
+        <x:v>     78.7835</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6279,7 +7554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.5672</x:v>
+        <x:v>     85.6130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6294,7 +7569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.7128</x:v>
+        <x:v>     96.0326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6309,7 +7584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4280</x:v>
+        <x:v>     99.5525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6324,7 +7599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.1432</x:v>
+        <x:v>    103.0958</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6339,7 +7614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.5736</x:v>
+        <x:v>    110.2524</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6354,7 +7629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.5800</x:v>
+        <x:v>    136.0368</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6369,7 +7644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.8712</x:v>
+        <x:v>    159.0489</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6384,7 +7659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.0360</x:v>
+        <x:v>    255.7543</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6399,7 +7674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    577.8104</x:v>
+        <x:v>    701.4080</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6414,7 +7689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.7256</x:v>
+        <x:v>    147.4377</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6429,7 +7704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    122.5336</x:v>
+        <x:v>    301.7382</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6444,7 +7719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.5736</x:v>
+        <x:v>    110.2524</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6459,7 +7734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7320</x:v>
+        <x:v>    174.8577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6474,7 +7749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.2888</x:v>
+        <x:v>    113.8658</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6489,7 +7764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.4408</x:v>
+        <x:v>    151.2848</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6504,7 +7779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0040</x:v>
+        <x:v>    117.5026</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6519,7 +7794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.5864</x:v>
+        <x:v>    162.9661</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6534,7 +7809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.1560</x:v>
+        <x:v>    155.1552</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6549,7 +7824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.0360</x:v>
+        <x:v>    255.7543</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6564,7 +7839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4280</x:v>
+        <x:v>     99.5525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6579,7 +7854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4280</x:v>
+        <x:v>     99.5525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6594,7 +7869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.1432</x:v>
+        <x:v>    103.0958</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6609,7 +7884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4280</x:v>
+        <x:v>     99.5525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6624,7 +7899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.2888</x:v>
+        <x:v>    113.8658</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6639,7 +7914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0040</x:v>
+        <x:v>    117.5026</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6654,7 +7929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.4408</x:v>
+        <x:v>    151.2848</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6669,7 +7944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    127.7072</x:v>
+        <x:v>    305.9734</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6684,7 +7959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     99.1752</x:v>
+        <x:v>    239.3233</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6699,7 +7974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.5736</x:v>
+        <x:v>    110.2524</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6714,7 +7989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.4472</x:v>
+        <x:v>    178.8683</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6729,7 +8004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.8648</x:v>
+        <x:v>    132.2832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6744,7 +8019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.1624</x:v>
+        <x:v>    182.9023</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6759,7 +8034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7320</x:v>
+        <x:v>    174.8577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6774,7 +8049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     87.1688</x:v>
+        <x:v>    210.9745</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6789,7 +8064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     87.1688</x:v>
+        <x:v>    210.9745</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6804,7 +8079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.4408</x:v>
+        <x:v>    151.2848</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6819,7 +8094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     87.1688</x:v>
+        <x:v>    210.9745</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6834,7 +8109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    634.7200</x:v>
+        <x:v>    754.4675</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6849,7 +8124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.3016</x:v>
+        <x:v>    166.9066</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6864,7 +8139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     88.8840</x:v>
+        <x:v>    214.9914</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6879,7 +8154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     94.0296</x:v>
+        <x:v>    227.1088</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6894,7 +8169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.7256</x:v>
+        <x:v>    147.4377</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6909,7 +8184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.7320</x:v>
+        <x:v>    174.8577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6924,7 +8199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.0168</x:v>
+        <x:v>    170.8705</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6939,7 +8214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.3016</x:v>
+        <x:v>    166.9066</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6954,7 +8229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     97.4600</x:v>
+        <x:v>    235.2412</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6969,7 +8244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.5928</x:v>
+        <x:v>    191.0403</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6984,7 +8259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    324.3040</x:v>
+        <x:v>    472.7446</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6999,7 +8274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.3080</x:v>
+        <x:v>    195.1444</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7014,7 +8289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    246.7000</x:v>
+        <x:v>    405.6445</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7029,7 +8304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    841.6640</x:v>
+        <x:v>    951.9603</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7044,7 +8319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.0104</x:v>
+        <x:v>    143.6141</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7059,7 +8334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.3016</x:v>
+        <x:v>    166.9066</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7074,7 +8349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    288.0888</x:v>
+        <x:v>    441.2412</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7089,7 +8364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.7384</x:v>
+        <x:v>    202.9749</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7104,7 +8379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.7384</x:v>
+        <x:v>    202.9749</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7119,7 +8394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.4408</x:v>
+        <x:v>    151.2848</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7134,7 +8409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.5928</x:v>
+        <x:v>    191.0403</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7149,7 +8424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    104.3208</x:v>
+        <x:v>    251.6313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7164,7 +8439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.4472</x:v>
+        <x:v>    178.8683</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7179,7 +8454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     88.8840</x:v>
+        <x:v>    214.9914</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7194,7 +8469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    205.3112</x:v>
+        <x:v>    370.5074</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7209,7 +8484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>   1033.0872</x:v>
+        <x:v>   1140.3010</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7224,7 +8499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    174.2696</x:v>
+        <x:v>    344.4743</x:v>
       </x:c>
     </x:row>
     <x:row>
